--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -507,30 +507,30 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.5</v>
+        <v>45520.65625</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18752</v>
+        <v>25178</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -556,39 +556,35 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.5</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>17924</v>
+        <v>15220</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -616,37 +612,37 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>lhUkVMh2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>15220</v>
+        <v>21029</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -674,37 +670,37 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>lhUkVMh2</t>
+          <t>IBmris38</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.66666666666</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25178</v>
+        <v>18523</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -729,36 +725,40 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.41666666666</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18523</v>
+        <v>17924</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -783,17 +783,17 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -802,21 +802,21 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20484</v>
+        <v>18752</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -841,21 +841,17 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -864,21 +860,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21029</v>
+        <v>20484</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -903,17 +899,21 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>4v0yqlWc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -922,21 +922,21 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>29778</v>
+        <v>33150</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -961,40 +961,40 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.65625</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>33150</v>
+        <v>29778</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1019,12 +1019,12 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,413 +507,413 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.5</v>
+        <v>45520.65625</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>55</v>
+      </c>
+      <c r="I2" t="n">
+        <v>551</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>0js8u60b</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>55</v>
+      </c>
+      <c r="I3" t="n">
+        <v>551</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>jqSiuc6F</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>55</v>
+      </c>
+      <c r="I4" t="n">
+        <v>551</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>fHYrsJy3</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45521.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>55</v>
+      </c>
+      <c r="I5" t="n">
+        <v>551</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ripawyyS</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45522.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>551</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>2NocJFqd</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
           <t xml:space="preserve">stade raymond kopa
   angers </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E7" t="n">
         <v>18752</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>SAlF91iL</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>IBmris38</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>55</v>
-      </c>
-      <c r="I2" t="n">
-        <v>551</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="H7" t="n">
+        <v>55</v>
+      </c>
+      <c r="I7" t="n">
+        <v>551</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>pfDZL71o</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>ripawyyS</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>M5VGwpVA</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
         <v>45522.5</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>17924</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>55</v>
-      </c>
-      <c r="I3" t="n">
-        <v>551</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0js8u60b</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>15220</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>55</v>
-      </c>
-      <c r="I4" t="n">
-        <v>551</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>SOLVXEbk</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>55</v>
-      </c>
-      <c r="I5" t="n">
-        <v>551</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>fHYrsJy3</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>55</v>
-      </c>
-      <c r="I6" t="n">
-        <v>551</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>M5VGwpVA</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de la mosson
   montpellier </t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E8" t="n">
         <v>20484</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Eyf00syR</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>nP6UzIU1</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>55</v>
-      </c>
-      <c r="I7" t="n">
-        <v>551</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="H8" t="n">
+        <v>55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>551</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>SblU3Hee</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>4v0yqlWc</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jqSiuc6F</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>21029</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>55</v>
-      </c>
-      <c r="I8" t="n">
-        <v>551</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -922,107 +922,629 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>55</v>
+      </c>
+      <c r="I9" t="n">
+        <v>551</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zkPwWhT1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45522.65625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
           <t xml:space="preserve">roazhon park
   rennes </t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" t="n">
         <v>29778</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>d2nnj1IE</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>2akflumR</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>55</v>
-      </c>
-      <c r="I9" t="n">
-        <v>551</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="H10" t="n">
+        <v>55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>551</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>veuetnGG</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>6ehlLyFq</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>MLmY2yB1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H16" t="n">
+        <v>55</v>
+      </c>
+      <c r="I16" t="n">
+        <v>551</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>551</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>551</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>55</v>
+      </c>
+      <c r="I19" t="n">
+        <v>551</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>55</v>
-      </c>
-      <c r="I10" t="n">
-        <v>551</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1026,528 +1026,6 @@
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>38223</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>55</v>
-      </c>
-      <c r="I11" t="n">
-        <v>551</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CKcVGr7E</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>55</v>
-      </c>
-      <c r="I12" t="n">
-        <v>551</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pSpI7vU0</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>59186</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>55</v>
-      </c>
-      <c r="I13" t="n">
-        <v>551</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>67394</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>55</v>
-      </c>
-      <c r="I14" t="n">
-        <v>551</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>35322</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>55</v>
-      </c>
-      <c r="I15" t="n">
-        <v>551</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>36178</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>55</v>
-      </c>
-      <c r="I16" t="n">
-        <v>551</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ppvl45N8</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>48229</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>55</v>
-      </c>
-      <c r="I17" t="n">
-        <v>551</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>55</v>
-      </c>
-      <c r="I18" t="n">
-        <v>551</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>55</v>
-      </c>
-      <c r="I19" t="n">
-        <v>551</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1026,6 +1026,470 @@
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45527.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45528.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45528.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45528.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45529.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>55</v>
+      </c>
+      <c r="I16" t="n">
+        <v>551</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>551</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>551</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,76 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -561,6 +631,48 @@
           <t>SblU3Hee</t>
         </is>
       </c>
+      <c r="P2" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>165</v>
+      </c>
+      <c r="U2" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>167</v>
+      </c>
+      <c r="W2" t="n">
+        <v>30</v>
+      </c>
+      <c r="X2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>74</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -619,6 +731,20 @@
           <t>YagoQJpq</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -677,6 +803,20 @@
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -731,6 +871,20 @@
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -789,6 +943,20 @@
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -847,6 +1015,20 @@
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -905,6 +1087,20 @@
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -967,6 +1163,20 @@
           <t>veuetnGG</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1025,6 +1235,20 @@
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1083,6 +1307,20 @@
           <t>4v0yqlWc</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1137,6 +1375,20 @@
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1199,6 +1451,20 @@
           <t>d2nnj1IE</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1257,6 +1523,20 @@
           <t>lhUkVMh2</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1319,6 +1599,20 @@
           <t>pfDZL71o</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1377,6 +1671,20 @@
           <t>2PIvr8o4</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1431,6 +1739,20 @@
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1489,6 +1811,20 @@
           <t>veuetnGG</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1547,6 +1883,20 @@
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.5</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">frappart s 
+          <t xml:space="preserve">pignard j 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>59186</v>
+        <v>38223</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -630,24 +630,38 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>179</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>298</v>
+      </c>
+      <c r="U2" t="n">
+        <v>28600000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>310</v>
+      </c>
       <c r="W2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="X2" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y2" t="n">
         <v>1</v>
@@ -656,10 +670,10 @@
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="AB2" t="n">
-        <v>2200000</v>
+        <v>11500000</v>
       </c>
       <c r="AC2" t="n">
         <v>82</v>
@@ -668,35 +682,35 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45529.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50186</v>
+        <v>35322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -723,85 +737,85 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>27.33333333333333</v>
+        <v>25.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>178</v>
+        <v>177.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.666666666666667</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>461</v>
+        <v>280</v>
       </c>
       <c r="U3" t="n">
-        <v>66800000</v>
+        <v>10425000</v>
       </c>
       <c r="V3" t="n">
-        <v>471</v>
+        <v>293</v>
       </c>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X3" t="n">
-        <v>176</v>
+        <v>181.6</v>
       </c>
       <c r="Y3" t="n">
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA3" t="n">
-        <v>131</v>
+        <v>322</v>
       </c>
       <c r="AB3" t="n">
-        <v>2325000</v>
+        <v>6050000</v>
       </c>
       <c r="AC3" t="n">
-        <v>144</v>
+        <v>363</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.66666666666</v>
+        <v>45529.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">batta f 
+          <t xml:space="preserve">dechepy b 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42000</v>
+        <v>36178</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -826,36 +840,888 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
+      <c r="P4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>179</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>308</v>
+      </c>
+      <c r="U4" t="n">
+        <v>52500000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>317</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>55</v>
+      </c>
+      <c r="I5" t="n">
+        <v>551</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>20</v>
+      </c>
+      <c r="X5" t="n">
+        <v>189</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>72</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45529.65625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>551</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>19</v>
       </c>
-      <c r="X4" t="n">
-        <v>188</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="Q6" t="n">
+        <v>179</v>
+      </c>
+      <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="AA4" t="n">
-        <v>64</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="T6" t="n">
+        <v>63</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="V6" t="n">
         <v>74</v>
       </c>
+      <c r="W6" t="n">
+        <v>21</v>
+      </c>
+      <c r="X6" t="n">
+        <v>180</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>74</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45534.65625</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>55</v>
+      </c>
+      <c r="I7" t="n">
+        <v>551</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>551</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>55</v>
+      </c>
+      <c r="I9" t="n">
+        <v>551</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>551</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45536.41666666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ChZKNjKb</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,109 +503,34 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.41666666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pignard j 
-  fra </t>
-        </is>
-      </c>
+        <v>45534.65625</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>38223</v>
+        <v>59186</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -630,87 +555,40 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>179</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T2" t="n">
-        <v>298</v>
-      </c>
-      <c r="U2" t="n">
-        <v>28600000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>310</v>
-      </c>
-      <c r="W2" t="n">
-        <v>21</v>
-      </c>
-      <c r="X2" t="n">
-        <v>180</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>76</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>11500000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>82</v>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">angoula g 
-  fra </t>
-        </is>
-      </c>
+        <v>45535.5</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>35322</v>
+        <v>15220</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -735,87 +613,36 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>177.5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>280</v>
-      </c>
-      <c r="U3" t="n">
-        <v>10425000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>293</v>
-      </c>
-      <c r="W3" t="n">
-        <v>22</v>
-      </c>
-      <c r="X3" t="n">
-        <v>181.6</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>322</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>6050000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>363</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dechepy b 
-  fra </t>
-        </is>
-      </c>
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36178</v>
+        <v>20484</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -842,71 +669,42 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>179</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>308</v>
-      </c>
-      <c r="U4" t="n">
-        <v>52500000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>317</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wattellier e 
-  fra </t>
-        </is>
-      </c>
+        <v>45535.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26109</v>
+        <v>33150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -931,77 +729,40 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>20</v>
-      </c>
-      <c r="X5" t="n">
-        <v>189</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>72</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>78</v>
+          <t>lhUkVMh2</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hhlQ5IbD</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45529.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ben el hadj salem h 
-  fra </t>
-        </is>
-      </c>
+        <v>45536.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>67394</v>
+        <v>18523</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1028,80 +789,42 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>179</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>63</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>74</v>
-      </c>
-      <c r="W6" t="n">
-        <v>21</v>
-      </c>
-      <c r="X6" t="n">
-        <v>180</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>74</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>9500000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>82</v>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45536.5</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>59186</v>
+        <v>18752</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1129,51 +852,37 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15220</v>
+        <v>25178</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1200,48 +909,34 @@
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20484</v>
+        <v>21029</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1266,58 +961,40 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+          <t>veuetnGG</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.66666666666</v>
+        <v>45536.65625</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>33150</v>
+        <v>50186</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1342,386 +1019,12 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IgtCPCkn</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45536.41666666666</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>IBmris38</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>55</v>
-      </c>
-      <c r="I11" t="n">
-        <v>551</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>SU02594U</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>18752</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>55</v>
-      </c>
-      <c r="I12" t="n">
-        <v>551</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>55</v>
-      </c>
-      <c r="I13" t="n">
-        <v>551</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>21029</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>55</v>
-      </c>
-      <c r="I14" t="n">
-        <v>551</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>55</v>
-      </c>
-      <c r="I15" t="n">
-        <v>551</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,34 +503,109 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45534.65625</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45535.5</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angoula g 
+  fra </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>59186</v>
+        <v>15220</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -556,39 +631,68 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>180</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>76</v>
+      </c>
+      <c r="U2" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>82</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.5</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>15220</v>
+        <v>20484</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -613,36 +717,91 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>196</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>74</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>74</v>
+      </c>
+      <c r="W3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>10425000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>293</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.58333333334</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45535.66666666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20484</v>
+        <v>33150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -667,44 +826,73 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
-        </is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>19</v>
+      </c>
+      <c r="X4" t="n">
+        <v>179</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>63</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.66666666666</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45536.41666666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>33150</v>
+        <v>18523</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -729,40 +917,91 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>lhUkVMh2</t>
-        </is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>173</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>66</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>82</v>
+      </c>
+      <c r="W5" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="X5" t="n">
+        <v>176</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>222</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>21100000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>233</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.41666666666</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45536.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18523</v>
+        <v>18752</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -787,44 +1026,87 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
-        </is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>176</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>131</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2325000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>144</v>
+      </c>
+      <c r="W6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>179</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>308</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>52500000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>317</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>45536.5</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18752</v>
+        <v>25178</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -850,39 +1132,82 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>188</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>64</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>74</v>
+      </c>
+      <c r="W7" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>330</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>7050000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>363</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>45536.5</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>25178</v>
+        <v>21029</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -908,35 +1233,86 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>180</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>74</v>
+      </c>
+      <c r="U8" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>82</v>
+      </c>
+      <c r="W8" t="n">
+        <v>20</v>
+      </c>
+      <c r="X8" t="n">
+        <v>189</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>72</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45536.65625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>21029</v>
+        <v>50186</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -961,70 +1337,54 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>55</v>
-      </c>
-      <c r="I10" t="n">
-        <v>551</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>IBmris38</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>383</v>
+      </c>
+      <c r="U9" t="n">
+        <v>47800000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>390</v>
+      </c>
+      <c r="W9" t="n">
+        <v>27</v>
+      </c>
+      <c r="X9" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>165</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>167</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45535.5</v>
+        <v>45536.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15220</v>
+        <v>18523</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -630,13 +630,21 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
       <c r="P2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q2" t="n">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -645,54 +653,68 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="U2" t="n">
-        <v>11500000</v>
+        <v>2200000</v>
       </c>
       <c r="V2" t="n">
         <v>82</v>
       </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="X2" t="n">
+        <v>176.3333333333333</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>222</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>18100000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>230</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">millot b 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20484</v>
+        <v>18752</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -717,91 +739,87 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="Q3" t="n">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
         <v>2</v>
       </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
       <c r="T3" t="n">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="U3" t="n">
-        <v>3500000</v>
+        <v>2325000</v>
       </c>
       <c r="V3" t="n">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="W3" t="n">
         <v>25.5</v>
       </c>
       <c r="X3" t="n">
-        <v>177.5</v>
+        <v>179</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="Z3" t="n">
         <v>4</v>
       </c>
       <c r="AA3" t="n">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="AB3" t="n">
-        <v>10425000</v>
+        <v>52500000</v>
       </c>
       <c r="AC3" t="n">
-        <v>293</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.66666666666</v>
+        <v>45536.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">frappart s 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>33150</v>
+        <v>25178</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -827,72 +845,82 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>188</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>64</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>74</v>
+      </c>
       <c r="W4" t="n">
-        <v>19</v>
+        <v>23.2</v>
       </c>
       <c r="X4" t="n">
-        <v>179</v>
+        <v>181.6</v>
       </c>
       <c r="Y4" t="n">
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA4" t="n">
-        <v>63</v>
+        <v>330</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000000</v>
+        <v>7050000</v>
       </c>
       <c r="AC4" t="n">
-        <v>74</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.41666666666</v>
+        <v>45536.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18523</v>
+        <v>21029</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -917,91 +945,87 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q5" t="n">
-        <v>173</v>
+        <v>177.5</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>66</v>
+        <v>149</v>
       </c>
       <c r="U5" t="n">
-        <v>2200000</v>
+        <v>16000000</v>
       </c>
       <c r="V5" t="n">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="W5" t="n">
-        <v>24.33333333333333</v>
+        <v>20</v>
       </c>
       <c r="X5" t="n">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="Y5" t="n">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>222</v>
+        <v>72</v>
       </c>
       <c r="AB5" t="n">
-        <v>21100000</v>
+        <v>2900000</v>
       </c>
       <c r="AC5" t="n">
-        <v>233</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18752</v>
+        <v>50186</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1026,363 +1050,52 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="n">
-        <v>176</v>
+        <v>177.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>383</v>
+      </c>
+      <c r="U6" t="n">
+        <v>47800000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>390</v>
+      </c>
+      <c r="W6" t="n">
+        <v>27</v>
+      </c>
+      <c r="X6" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2</v>
       </c>
-      <c r="T6" t="n">
-        <v>131</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2325000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>144</v>
-      </c>
-      <c r="W6" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X6" t="n">
-        <v>179</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4</v>
-      </c>
       <c r="AA6" t="n">
-        <v>308</v>
+        <v>165</v>
       </c>
       <c r="AB6" t="n">
-        <v>52500000</v>
+        <v>68000000</v>
       </c>
       <c r="AC6" t="n">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>55</v>
-      </c>
-      <c r="I7" t="n">
-        <v>551</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>188</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>64</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>74</v>
-      </c>
-      <c r="W7" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>181.6</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>330</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>7050000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>21029</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>55</v>
-      </c>
-      <c r="I8" t="n">
-        <v>551</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>180</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>74</v>
-      </c>
-      <c r="U8" t="n">
-        <v>9500000</v>
-      </c>
-      <c r="V8" t="n">
-        <v>82</v>
-      </c>
-      <c r="W8" t="n">
-        <v>20</v>
-      </c>
-      <c r="X8" t="n">
-        <v>189</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>72</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>55</v>
-      </c>
-      <c r="I9" t="n">
-        <v>551</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>177.4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>383</v>
-      </c>
-      <c r="U9" t="n">
-        <v>47800000</v>
-      </c>
-      <c r="V9" t="n">
-        <v>390</v>
-      </c>
-      <c r="W9" t="n">
-        <v>27</v>
-      </c>
-      <c r="X9" t="n">
-        <v>186.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>165</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>68000000</v>
-      </c>
-      <c r="AC9" t="n">
         <v>167</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,109 +503,34 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>vsYzkTIc</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.41666666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
-        </is>
-      </c>
+        <v>45548.65625</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18523</v>
+        <v>42000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -630,86 +555,35 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>173</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>66</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>82</v>
-      </c>
-      <c r="W2" t="n">
-        <v>26.33333333333333</v>
-      </c>
-      <c r="X2" t="n">
-        <v>176.3333333333333</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>222</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>18100000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>230</v>
+          <t>IBmris38</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>0dMqm7mA</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stinat j 
-  fra </t>
-        </is>
-      </c>
+        <v>45549.5</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>18752</v>
+        <v>67394</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -739,87 +613,44 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>2PIvr8o4</t>
         </is>
-      </c>
-      <c r="P3" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>176</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2</v>
-      </c>
-      <c r="T3" t="n">
-        <v>131</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2325000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>144</v>
-      </c>
-      <c r="W3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>179</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>308</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>52500000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>317</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>CGH7Enso</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
+        <v>45549.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25178</v>
+        <v>17924</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -845,82 +676,39 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>188</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>64</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>74</v>
-      </c>
-      <c r="W4" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>181.6</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>330</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>7050000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>363</v>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>8MPiooIM</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">parc des princes
+  paris </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21029</v>
+        <v>48229</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -946,86 +734,35 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>177.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>149</v>
-      </c>
-      <c r="U5" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>159</v>
-      </c>
-      <c r="W5" t="n">
-        <v>20</v>
-      </c>
-      <c r="X5" t="n">
-        <v>189</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>72</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>78</v>
-      </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6ZfxDZ5t</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
-        </is>
-      </c>
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>50186</v>
+        <v>29778</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1052,52 +789,242 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>55</v>
+      </c>
+      <c r="I7" t="n">
+        <v>551</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>551</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>55</v>
+      </c>
+      <c r="I9" t="n">
+        <v>551</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Qw81zU34</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.65625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>IBmris38</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>177.4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>383</v>
-      </c>
-      <c r="U6" t="n">
-        <v>47800000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>390</v>
-      </c>
-      <c r="W6" t="n">
-        <v>27</v>
-      </c>
-      <c r="X6" t="n">
-        <v>186.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>165</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>68000000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>167</v>
-      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>551</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1026,6 +1026,528 @@
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0K4Ww3Ad</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45555.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45556.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45556.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>55</v>
+      </c>
+      <c r="I16" t="n">
+        <v>551</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>551</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>551</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>55</v>
+      </c>
+      <c r="I19" t="n">
+        <v>551</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,39 +503,109 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0K4Ww3Ad</t>
+          <t>fiy8wfGD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45555.65625</v>
+        <v>45556.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">brisard j 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>36178</v>
+        <v>50186</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -562,38 +632,89 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>289</v>
+      </c>
+      <c r="U2" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>319</v>
+      </c>
+      <c r="W2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>183</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fiy8wfGD</t>
+          <t>noOg1c8K</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45556.5</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45556.58333333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50186</v>
+        <v>29778</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -620,47 +741,89 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
-        </is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>189</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>72</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>78</v>
+      </c>
+      <c r="W3" t="n">
+        <v>29</v>
+      </c>
+      <c r="X3" t="n">
+        <v>164</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>72</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>noOg1c8K</t>
+          <t>v39B1623</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45556.58333333334</v>
+        <v>45556.66666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">pignard j 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>29778</v>
+        <v>21029</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -685,49 +848,83 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>149</v>
+      </c>
+      <c r="U4" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>159</v>
+      </c>
+      <c r="W4" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X4" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>419</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>242000000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>426</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v39B1623</t>
+          <t>6V4QeyWs</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45556.66666666666</v>
+        <v>45557.41666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pignard j 
+          <t xml:space="preserve">frappart s 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21029</v>
+        <v>18523</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -752,41 +949,87 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>183</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>140</v>
+      </c>
+      <c r="U5" t="n">
+        <v>10200000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>164</v>
+      </c>
+      <c r="W5" t="n">
+        <v>19</v>
+      </c>
+      <c r="X5" t="n">
+        <v>188</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6V4QeyWs</t>
+          <t>6HPisxHl</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45557.41666666666</v>
+        <v>45557.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">frappart s 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18523</v>
+        <v>18752</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -811,17 +1054,59 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>130</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>143</v>
+      </c>
+      <c r="W6" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="X6" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>221</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>13200000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>225</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6HPisxHl</t>
+          <t>nTCJapXF</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -829,27 +1114,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
+          <t xml:space="preserve">batta f 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18752</v>
+        <v>15220</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -875,16 +1160,40 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>183</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>154</v>
+      </c>
+      <c r="U7" t="n">
+        <v>23500000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>160</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nTCJapXF</t>
+          <t>EsTauGo1</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -892,27 +1201,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">batta f 
+          <t xml:space="preserve">ben el hadj salem h 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15220</v>
+        <v>20484</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -937,41 +1246,87 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>185.6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>358</v>
+      </c>
+      <c r="U8" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>383</v>
+      </c>
+      <c r="W8" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="X8" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>199</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4450000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>223</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EsTauGo1</t>
+          <t>S66OuPup</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45557.5</v>
+        <v>45557.65625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ben el hadj salem h 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20484</v>
+        <v>59186</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -996,596 +1351,39 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>S66OuPup</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45557.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>59186</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>55</v>
-      </c>
-      <c r="I10" t="n">
-        <v>551</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
         <is>
           <t>lhUkVMh2</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>MRfkjXaJ</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45562.58333333334</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>17924</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>55</v>
-      </c>
-      <c r="I11" t="n">
-        <v>551</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>zBdshgV6</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45562.66666666666</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>48229</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>55</v>
-      </c>
-      <c r="I12" t="n">
-        <v>551</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>v3PZcqJP</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45563.5</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>38223</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>55</v>
-      </c>
-      <c r="I13" t="n">
-        <v>551</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>xb7MlutC</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45563.58333333334</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>55</v>
-      </c>
-      <c r="I14" t="n">
-        <v>551</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45563.66666666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>55</v>
-      </c>
-      <c r="I15" t="n">
-        <v>551</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>55</v>
-      </c>
-      <c r="I16" t="n">
-        <v>551</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45564.5</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>18752</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>55</v>
-      </c>
-      <c r="I17" t="n">
-        <v>551</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45564.5</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>35322</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>55</v>
-      </c>
-      <c r="I18" t="n">
-        <v>551</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>55</v>
-      </c>
-      <c r="I19" t="n">
-        <v>551</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>lhUkVMh2</t>
-        </is>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>20</v>
+      </c>
+      <c r="X9" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>137</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,66 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -513,7 +573,12 @@
       <c r="B2" s="2" t="n">
         <v>45562.58333333334</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de l abbe deschamps
@@ -557,6 +622,40 @@
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>129</v>
+      </c>
+      <c r="V2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>183</v>
+      </c>
+      <c r="X2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>16500</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -567,7 +666,12 @@
       <c r="B3" s="2" t="n">
         <v>45562.66666666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">parc des princes
@@ -614,6 +718,42 @@
         <is>
           <t>veuetnGG</t>
         </is>
+      </c>
+      <c r="P3" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>185</v>
+      </c>
+      <c r="R3" t="n">
+        <v>82.66666666666667</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100333.3333333333</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>248</v>
+      </c>
+      <c r="V3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W3" t="n">
+        <v>189</v>
+      </c>
+      <c r="X3" t="n">
+        <v>72</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="4">
@@ -625,7 +765,12 @@
       <c r="B4" s="2" t="n">
         <v>45563.5</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">stade bollaert delelis
@@ -676,6 +821,42 @@
         <is>
           <t>2PIvr8o4</t>
         </is>
+      </c>
+      <c r="P4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="R4" t="n">
+        <v>75.33333333333333</v>
+      </c>
+      <c r="S4" t="n">
+        <v>36000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>226</v>
+      </c>
+      <c r="V4" t="n">
+        <v>27</v>
+      </c>
+      <c r="W4" t="n">
+        <v>183</v>
+      </c>
+      <c r="X4" t="n">
+        <v>77</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>52333.33333333334</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>231</v>
       </c>
     </row>
     <row r="5">
@@ -687,7 +868,12 @@
       <c r="B5" s="2" t="n">
         <v>45563.58333333334</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dechepy b 
+  fra </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">stade oceane
@@ -734,6 +920,42 @@
         <is>
           <t>IBmris38</t>
         </is>
+      </c>
+      <c r="P5" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>188</v>
+      </c>
+      <c r="R5" t="n">
+        <v>64</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>64</v>
+      </c>
+      <c r="V5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>28000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>305</v>
       </c>
     </row>
     <row r="6">
@@ -745,7 +967,12 @@
       <c r="B6" s="2" t="n">
         <v>45563.66666666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">stade louis ii
@@ -796,6 +1023,42 @@
         <is>
           <t>SblU3Hee</t>
         </is>
+      </c>
+      <c r="P6" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>183</v>
+      </c>
+      <c r="R6" t="n">
+        <v>70</v>
+      </c>
+      <c r="S6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>140</v>
+      </c>
+      <c r="V6" t="n">
+        <v>26</v>
+      </c>
+      <c r="W6" t="n">
+        <v>184</v>
+      </c>
+      <c r="X6" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>14750</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>290</v>
       </c>
     </row>
     <row r="7">
@@ -807,7 +1070,12 @@
       <c r="B7" s="2" t="n">
         <v>45564.41666666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angoula g 
+  fra </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">stadium municipal
@@ -851,6 +1119,18 @@
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -861,7 +1141,12 @@
       <c r="B8" s="2" t="n">
         <v>45564.5</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">stade raymond kopa
@@ -905,6 +1190,40 @@
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>263</v>
+      </c>
+      <c r="V8" t="n">
+        <v>26</v>
+      </c>
+      <c r="W8" t="n">
+        <v>193</v>
+      </c>
+      <c r="X8" t="n">
+        <v>74</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -915,7 +1234,12 @@
       <c r="B9" s="2" t="n">
         <v>45564.5</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de la beaujoire
@@ -963,6 +1287,42 @@
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>177.3333333333333</v>
+      </c>
+      <c r="R9" t="n">
+        <v>73</v>
+      </c>
+      <c r="S9" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>219</v>
+      </c>
+      <c r="V9" t="n">
+        <v>28</v>
+      </c>
+      <c r="W9" t="n">
+        <v>180</v>
+      </c>
+      <c r="X9" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5250</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>280</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -973,7 +1333,12 @@
       <c r="B10" s="2" t="n">
         <v>45564.65625</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de la meinau
@@ -1025,528 +1390,40 @@
           <t>lhUkVMh2</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>xYNVFHvB</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45569.65625</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>67394</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>55</v>
-      </c>
-      <c r="I11" t="n">
-        <v>551</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>z9REJaun</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45570.5</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>55</v>
-      </c>
-      <c r="I12" t="n">
-        <v>551</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Wf14adfU</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45570.58333333334</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>55</v>
-      </c>
-      <c r="I13" t="n">
-        <v>551</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8Kp3c9Oq</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45570.66666666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>29778</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>55</v>
-      </c>
-      <c r="I14" t="n">
-        <v>551</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IHSe3ve5</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>59186</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>55</v>
-      </c>
-      <c r="I15" t="n">
-        <v>551</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>rZUMHwAb</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>15220</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>55</v>
-      </c>
-      <c r="I16" t="n">
-        <v>551</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WhWcJjo3</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>21029</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>55</v>
-      </c>
-      <c r="I17" t="n">
-        <v>551</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>4nvCemgd</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>55</v>
-      </c>
-      <c r="I18" t="n">
-        <v>551</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>OUcd1IPH</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45571.65625</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>36178</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>55</v>
-      </c>
-      <c r="I19" t="n">
-        <v>551</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>183</v>
+      </c>
+      <c r="R10" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>129</v>
+      </c>
+      <c r="V10" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="W10" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>49500</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>293</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,35 +567,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MRfkjXaJ</t>
+          <t>bDeVnJAO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45562.58333333334</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17924</v>
+        <v>33150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -622,73 +622,51 @@
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>64.5</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>129</v>
-      </c>
-      <c r="V2" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>183</v>
-      </c>
-      <c r="X2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>16500</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>154</v>
-      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zBdshgV6</t>
+          <t>p4Um50Qh</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45562.66666666666</v>
+        <v>45564.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ben el hadj salem h 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48229</v>
+        <v>18752</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -714,80 +692,74 @@
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>27</v>
+        <v>22.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>185</v>
+        <v>180.5</v>
       </c>
       <c r="R3" t="n">
-        <v>82.66666666666667</v>
-      </c>
-      <c r="S3" t="n">
-        <v>100333.3333333333</v>
-      </c>
+        <v>65.75</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="V3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="W3" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="X3" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y3" t="n">
-        <v>14000</v>
+        <v>19000</v>
       </c>
       <c r="Z3" t="n">
         <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>v3PZcqJP</t>
+          <t>zZA5hNtm</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.5</v>
+        <v>45564.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">kherradji a 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38223</v>
+        <v>35322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -814,83 +786,79 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>25</v>
+        <v>26.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>180.3333333333333</v>
+        <v>179.8</v>
       </c>
       <c r="R4" t="n">
-        <v>75.33333333333333</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>36000</v>
+        <v>18400</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>226</v>
+        <v>362</v>
       </c>
       <c r="V4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W4" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="X4" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="Y4" t="n">
-        <v>52333.33333333334</v>
+        <v>5250</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA4" t="n">
-        <v>231</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xb7MlutC</t>
+          <t>Ee8YgF0f</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45563.58333333334</v>
+        <v>45564.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">dechepy b 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25178</v>
+        <v>26109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -915,513 +883,48 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>lhUkVMh2</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="R5" t="n">
-        <v>64</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3000</v>
-      </c>
+        <v>64.5</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="V5" t="n">
-        <v>27.5</v>
+        <v>22.75</v>
       </c>
       <c r="W5" t="n">
-        <v>181.5</v>
+        <v>182.5</v>
       </c>
       <c r="X5" t="n">
-        <v>76.25</v>
+        <v>73.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>28000</v>
+        <v>49500</v>
       </c>
       <c r="Z5" t="n">
         <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45563.66666666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>55</v>
-      </c>
-      <c r="I6" t="n">
-        <v>551</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>183</v>
-      </c>
-      <c r="R6" t="n">
-        <v>70</v>
-      </c>
-      <c r="S6" t="n">
-        <v>14500</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>140</v>
-      </c>
-      <c r="V6" t="n">
-        <v>26</v>
-      </c>
-      <c r="W6" t="n">
-        <v>184</v>
-      </c>
-      <c r="X6" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>14750</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">angoula g 
-  fra </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>55</v>
-      </c>
-      <c r="I7" t="n">
-        <v>551</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45564.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wattellier e 
-  fra </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>18752</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>55</v>
-      </c>
-      <c r="I8" t="n">
-        <v>551</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>180.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>65.75</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>263</v>
-      </c>
-      <c r="V8" t="n">
-        <v>26</v>
-      </c>
-      <c r="W8" t="n">
-        <v>193</v>
-      </c>
-      <c r="X8" t="n">
-        <v>74</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>19000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45564.5</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kherradji a 
-  fra </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>35322</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>55</v>
-      </c>
-      <c r="I9" t="n">
-        <v>551</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>27.33333333333333</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>177.3333333333333</v>
-      </c>
-      <c r="R9" t="n">
-        <v>73</v>
-      </c>
-      <c r="S9" t="n">
-        <v>18000</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>219</v>
-      </c>
-      <c r="V9" t="n">
-        <v>28</v>
-      </c>
-      <c r="W9" t="n">
-        <v>180</v>
-      </c>
-      <c r="X9" t="n">
-        <v>70</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>5250</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>55</v>
-      </c>
-      <c r="I10" t="n">
-        <v>551</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>183</v>
-      </c>
-      <c r="R10" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>129</v>
-      </c>
-      <c r="V10" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="W10" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>73.25</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>49500</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA10" t="n">
         <v>293</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,42 +495,42 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home_rival_team</t>
+          <t>mean_age_player_miss_home</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away_rival_team</t>
+          <t>mean_hei_player_miss_home</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>n_player_miss_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>sum_rat_player_miss_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_miss_home</t>
+          <t>sum_wage_player_miss_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_miss_home</t>
+          <t>sum_value_player_miss_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>sum_pot_player_miss_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_rep_player_miss_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
@@ -545,57 +545,67 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_miss_away</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_miss_away</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>sum_wage_player_miss_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDeVnJAO</t>
+          <t>xYNVFHvB</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45569.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>33150</v>
+        <v>67394</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -628,45 +638,61 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="W2" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>188</v>
+      </c>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>217</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p4Um50Qh</t>
+          <t>z9REJaun</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.5</v>
+        <v>45570.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>18752</v>
+        <v>42000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -691,75 +717,85 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>28</v>
+      </c>
+      <c r="O3" t="n">
+        <v>180.25</v>
+      </c>
       <c r="P3" t="n">
-        <v>22.75</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>180.5</v>
+        <v>280</v>
       </c>
       <c r="R3" t="n">
-        <v>65.75</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>21000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6675000</v>
+      </c>
       <c r="T3" t="n">
+        <v>284</v>
+      </c>
+      <c r="U3" t="n">
         <v>4</v>
       </c>
-      <c r="U3" t="n">
-        <v>263</v>
-      </c>
       <c r="V3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="W3" t="n">
-        <v>193</v>
+        <v>186.5</v>
       </c>
       <c r="X3" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="n">
-        <v>19000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>74</v>
+        <v>2350000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>149</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zZA5hNtm</t>
+          <t>Wf14adfU</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45564.5</v>
+        <v>45570.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>35322</v>
+        <v>50186</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -784,149 +820,560 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>28</v>
+      </c>
+      <c r="O4" t="n">
+        <v>187</v>
+      </c>
       <c r="P4" t="n">
-        <v>26.8</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>179.8</v>
+        <v>75</v>
       </c>
       <c r="R4" t="n">
-        <v>72.40000000000001</v>
+        <v>9000</v>
       </c>
       <c r="S4" t="n">
-        <v>18400</v>
+        <v>5500000</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="U4" t="n">
-        <v>362</v>
-      </c>
-      <c r="V4" t="n">
-        <v>28</v>
-      </c>
-      <c r="W4" t="n">
-        <v>180</v>
-      </c>
-      <c r="X4" t="n">
-        <v>70</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>5250</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>280</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ee8YgF0f</t>
+          <t>8Kp3c9Oq</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45564.65625</v>
+        <v>45570.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>55</v>
+      </c>
+      <c r="I5" t="n">
+        <v>551</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>551</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>55</v>
+      </c>
+      <c r="I7" t="n">
+        <v>551</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>551</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de la meinau
   strasbourg </t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E9" t="n">
         <v>26109</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>nP6UzIU1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>55</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I9" t="n">
         <v>551</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K9" t="n">
         <v>20242025</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>183</v>
-      </c>
-      <c r="R5" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>129</v>
-      </c>
-      <c r="V5" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="W5" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>73.25</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>49500</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>293</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>20</v>
+      </c>
+      <c r="W9" t="n">
+        <v>184</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>76</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>551</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45583.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,80 +495,40 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_age_player_miss_away</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_hei_player_miss_away</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>sum_wage_player_miss_home</t>
+          <t>sum_wage_player_miss_away</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>sum_value_player_miss_home</t>
+          <t>sum_value_player_miss_away</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>sum_pot_player_miss_away</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
         </is>
@@ -577,35 +537,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xYNVFHvB</t>
+          <t>IHSe3ve5</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.65625</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>67394</v>
+        <v>59186</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -638,61 +598,39 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>21.66666666666667</v>
-      </c>
-      <c r="W2" t="n">
-        <v>182.6666666666667</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>188</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>217</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>z9REJaun</t>
+          <t>rZUMHwAb</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.5</v>
+        <v>45571.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>42000</v>
+        <v>15220</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -717,85 +655,47 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>28</v>
-      </c>
-      <c r="O3" t="n">
-        <v>180.25</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>280</v>
-      </c>
-      <c r="R3" t="n">
-        <v>21000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6675000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>284</v>
-      </c>
-      <c r="U3" t="n">
-        <v>4</v>
-      </c>
-      <c r="V3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W3" t="n">
-        <v>186.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>129</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="n">
-        <v>2350000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>149</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Wf14adfU</t>
+          <t>WhWcJjo3</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.58333333334</v>
+        <v>45571.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">turpin c 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>50186</v>
+        <v>21029</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -820,71 +720,47 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>28</v>
-      </c>
-      <c r="O4" t="n">
-        <v>187</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>75</v>
-      </c>
-      <c r="R4" t="n">
-        <v>9000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>76</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
+          <t>4nvCemgd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.66666666666</v>
+        <v>45571.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">frappart s 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>29778</v>
+        <v>26109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -909,55 +785,63 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>20</v>
+      </c>
+      <c r="O5" t="n">
+        <v>184</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>64</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>76</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45571.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bollengier m 
+          <t xml:space="preserve">brisard j 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>59186</v>
+        <v>36178</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -990,47 +874,34 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millot b 
-  fra </t>
-        </is>
-      </c>
+        <v>45583.65625</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15220</v>
+        <v>18523</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1063,47 +934,34 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
-        </is>
-      </c>
+        <v>45584.5</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21029</v>
+        <v>15220</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1136,42 +994,29 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frappart s 
-  fra </t>
-        </is>
-      </c>
+        <v>45584.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>26109</v>
+        <v>42000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1209,63 +1054,34 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>20</v>
-      </c>
-      <c r="W9" t="n">
-        <v>184</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>64</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>76</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brisard j 
-  fra </t>
-        </is>
-      </c>
+        <v>45584.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
+          <t xml:space="preserve">parc des princes
+  paris </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>36178</v>
+        <v>48229</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1298,42 +1114,34 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45583.65625</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18523</v>
+        <v>25178</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1366,14 +1174,246 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>h8K6HUFF</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WMcg8Qx2</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vPIEF8pS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>nVutWTU8</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45585.65625</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,86 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -550,6 +630,38 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>28</v>
+      </c>
+      <c r="W2" t="n">
+        <v>187</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>76</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -607,6 +719,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -664,6 +792,38 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N4" t="n">
+        <v>28</v>
+      </c>
+      <c r="O4" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>280</v>
+      </c>
+      <c r="R4" t="n">
+        <v>21000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6675000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>284</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -721,6 +881,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -778,6 +954,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -835,6 +1027,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -892,6 +1100,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -949,6 +1173,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1006,6 +1246,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1058,6 +1314,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1110,6 +1382,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1162,6 +1450,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1214,6 +1518,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1266,6 +1586,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1318,6 +1654,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1370,6 +1722,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1422,6 +1790,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1474,6 +1858,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,479 +493,982 @@
           <t>competition</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>lYpTkOLs</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45590.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">batta f 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>55</v>
+      </c>
+      <c r="I2" t="n">
+        <v>551</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>p0vxl2jf</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45591.5</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>55</v>
+      </c>
+      <c r="I3" t="n">
+        <v>551</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>hQspntL6</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45591.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>55</v>
+      </c>
+      <c r="I4" t="n">
+        <v>551</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>vaZNtoqR</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45591.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>55</v>
+      </c>
+      <c r="I5" t="n">
+        <v>551</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WdE2Z2y1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>551</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>55</v>
+      </c>
+      <c r="I7" t="n">
+        <v>551</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>551</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>55</v>
+      </c>
+      <c r="I9" t="n">
+        <v>551</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.69791666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>551</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45597.625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45597.70833333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.54166666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.625</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>vuBo4Eth</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.70833333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>55</v>
+      </c>
+      <c r="I16" t="n">
+        <v>551</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45599.54166666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>551</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45599.54166666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">stade oceane
   le havre </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E18" t="n">
         <v>25178</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>CIEe04GT</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>55</v>
-      </c>
-      <c r="I2" t="n">
-        <v>551</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>h8K6HUFF</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45585.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">batta f 
-  fra </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>17924</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>55</v>
-      </c>
-      <c r="I3" t="n">
-        <v>551</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>185.8</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>328</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>6150000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>359</v>
-      </c>
-      <c r="U3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>WMcg8Qx2</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45585.5</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">angoula g 
-  fra </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>551</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>UTsToXQN</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45599.69791666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de la beaujoire
   nantes </t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E19" t="n">
         <v>35322</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>veuetnGG</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>55</v>
-      </c>
-      <c r="I4" t="n">
-        <v>551</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>vPIEF8pS</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45585.5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>55</v>
-      </c>
-      <c r="I5" t="n">
-        <v>551</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="W5" t="n">
-        <v>182</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>260</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>289</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>nVutWTU8</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45585.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">turpin c 
-  fra </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>20484</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>SblU3Hee</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>55</v>
-      </c>
-      <c r="I6" t="n">
-        <v>551</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>55</v>
+      </c>
+      <c r="I19" t="n">
+        <v>551</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,86 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -550,6 +630,38 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N2" t="n">
+        <v>20</v>
+      </c>
+      <c r="O2" t="n">
+        <v>189</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>72</v>
+      </c>
+      <c r="R2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>78</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -607,6 +719,52 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N3" t="n">
+        <v>23.83333333333333</v>
+      </c>
+      <c r="O3" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>397</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>436</v>
+      </c>
+      <c r="U3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" t="n">
+        <v>28</v>
+      </c>
+      <c r="W3" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>280</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>21000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>6675000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>284</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -664,6 +822,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -721,6 +895,38 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>28</v>
+      </c>
+      <c r="W5" t="n">
+        <v>187</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>76</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -778,6 +984,38 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>24</v>
+      </c>
+      <c r="W6" t="n">
+        <v>187</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>138</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>152</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -788,7 +1026,12 @@
       <c r="B7" s="2" t="n">
         <v>45592.54166666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de la mosson
@@ -830,6 +1073,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -887,6 +1146,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -944,6 +1219,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1001,474 +1292,22 @@
           <t>ligue 1</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>0ljCkFRb</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45597.625</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>55</v>
-      </c>
-      <c r="I11" t="n">
-        <v>551</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>bqYbtBlo</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45597.70833333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>55</v>
-      </c>
-      <c r="I12" t="n">
-        <v>551</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>rX720WuH</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45598.54166666666</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>48229</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>55</v>
-      </c>
-      <c r="I13" t="n">
-        <v>551</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>n5Eg2hB4</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45598.625</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>15220</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>55</v>
-      </c>
-      <c r="I14" t="n">
-        <v>551</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>vuBo4Eth</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45598.70833333334</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>55</v>
-      </c>
-      <c r="I15" t="n">
-        <v>551</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4Md3iycn</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45599.45833333334</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>55</v>
-      </c>
-      <c r="I16" t="n">
-        <v>551</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>EuWhpKkJ</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45599.54166666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>17924</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>55</v>
-      </c>
-      <c r="I17" t="n">
-        <v>551</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Y1lKmgdB</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45599.54166666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>55</v>
-      </c>
-      <c r="I18" t="n">
-        <v>551</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UTsToXQN</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45599.69791666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>35322</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>55</v>
-      </c>
-      <c r="I19" t="n">
-        <v>551</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,86 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -550,6 +630,36 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>23.83333333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>397</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>436</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -607,6 +717,38 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N3" t="n">
+        <v>28</v>
+      </c>
+      <c r="O3" t="n">
+        <v>187</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>75</v>
+      </c>
+      <c r="R3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>76</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -664,6 +806,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -721,6 +879,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -778,6 +952,38 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N6" t="n">
+        <v>28</v>
+      </c>
+      <c r="O6" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>280</v>
+      </c>
+      <c r="R6" t="n">
+        <v>21000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6675000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>284</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -835,6 +1041,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -892,6 +1114,54 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N8" t="n">
+        <v>24</v>
+      </c>
+      <c r="O8" t="n">
+        <v>186</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>198</v>
+      </c>
+      <c r="R8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>219</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>20</v>
+      </c>
+      <c r="W8" t="n">
+        <v>189</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>72</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>14000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>78</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -949,6 +1219,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1006,474 +1292,22 @@
           <t>ligue 1</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Gp6AbAAT</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45604.69791666666</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>67394</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>55</v>
-      </c>
-      <c r="I11" t="n">
-        <v>551</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>figxD9PM</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45605.54166666666</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>55</v>
-      </c>
-      <c r="I12" t="n">
-        <v>551</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>bJl87mmp</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45605.625</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>38223</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>55</v>
-      </c>
-      <c r="I13" t="n">
-        <v>551</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dYK8BH5F</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45605.70833333334</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>18752</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>55</v>
-      </c>
-      <c r="I14" t="n">
-        <v>551</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>l8H0Dwy3</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45606.45833333334</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>36178</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>55</v>
-      </c>
-      <c r="I15" t="n">
-        <v>551</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>nRkUEVfA</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45606.54166666666</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>55</v>
-      </c>
-      <c r="I16" t="n">
-        <v>551</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QB1LGiQc</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45606.54166666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>20484</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>55</v>
-      </c>
-      <c r="I17" t="n">
-        <v>551</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>WWnG5RHd</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45606.54166666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>29778</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>55</v>
-      </c>
-      <c r="I18" t="n">
-        <v>551</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>b59ZhlYj</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45606.69791666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>59186</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>55</v>
-      </c>
-      <c r="I19" t="n">
-        <v>551</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,119 +493,39 @@
           <t>competition</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0ljCkFRb</t>
+          <t>Gp6AbAAT</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45597.625</v>
+        <v>45604.69791666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18523</v>
+        <v>67394</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -629,70 +549,40 @@
         <is>
           <t>ligue 1</t>
         </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>23.83333333333333</v>
-      </c>
-      <c r="W2" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>397</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>7900000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>436</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bqYbtBlo</t>
+          <t>figxD9PM</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45597.70833333334</v>
+        <v>45605.54166666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">dechepy b 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50186</v>
+        <v>26109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -717,71 +607,39 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>28</v>
-      </c>
-      <c r="O3" t="n">
-        <v>187</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>75</v>
-      </c>
-      <c r="R3" t="n">
-        <v>9000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>76</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rX720WuH</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.54166666666</v>
+        <v>45605.625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48229</v>
+        <v>38223</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -806,55 +664,39 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n5Eg2hB4</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45598.625</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">turpin c 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15220</v>
+        <v>18752</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -879,55 +721,39 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vuBo4Eth</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.70833333334</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>42000</v>
+        <v>36178</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -952,66 +778,34 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>28</v>
-      </c>
-      <c r="O6" t="n">
-        <v>180.25</v>
-      </c>
-      <c r="P6" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>280</v>
-      </c>
-      <c r="R6" t="n">
-        <v>21000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>6675000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>284</v>
-      </c>
-      <c r="U6" t="n">
-        <v>4</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4Md3iycn</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.45833333334</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
+          <t xml:space="preserve">ben el hadj salem h 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>33150</v>
+        <v>25178</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1041,55 +835,39 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EuWhpKkJ</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.54166666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
+          <t xml:space="preserve">pignard j 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>17924</v>
+        <v>20484</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1113,88 +891,40 @@
         <is>
           <t>ligue 1</t>
         </is>
-      </c>
-      <c r="N8" t="n">
-        <v>24</v>
-      </c>
-      <c r="O8" t="n">
-        <v>186</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>198</v>
-      </c>
-      <c r="R8" t="n">
-        <v>9000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>219</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" t="n">
-        <v>20</v>
-      </c>
-      <c r="W8" t="n">
-        <v>189</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>72</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>14000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>78</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Y1lKmgdB</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45599.54166666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">frappart s 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>25178</v>
+        <v>29778</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1219,55 +949,39 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UTsToXQN</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45599.69791666666</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">dechepy b 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>35322</v>
+        <v>59186</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1292,22 +1006,6 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,86 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -550,6 +630,52 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N2" t="n">
+        <v>18</v>
+      </c>
+      <c r="O2" t="n">
+        <v>185</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>64</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>84</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>24</v>
+      </c>
+      <c r="W2" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>330</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>7850000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>366</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -607,6 +733,38 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>158</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>175000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>56500000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>168</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -664,6 +822,54 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N4" t="n">
+        <v>26</v>
+      </c>
+      <c r="O4" t="n">
+        <v>185</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>78</v>
+      </c>
+      <c r="R4" t="n">
+        <v>57000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>79</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>27</v>
+      </c>
+      <c r="W4" t="n">
+        <v>182</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>14000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>71</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -721,6 +927,36 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>330</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>359</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -778,6 +1014,38 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>31</v>
+      </c>
+      <c r="W6" t="n">
+        <v>191</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>76</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>36000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>76</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -835,6 +1103,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -892,6 +1176,22 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -949,6 +1249,38 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N9" t="n">
+        <v>20</v>
+      </c>
+      <c r="O9" t="n">
+        <v>189</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>72</v>
+      </c>
+      <c r="R9" t="n">
+        <v>14000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>78</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1006,6 +1338,326 @@
           <t>ligue 1</t>
         </is>
       </c>
+      <c r="N10" t="n">
+        <v>34</v>
+      </c>
+      <c r="O10" t="n">
+        <v>194</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>81</v>
+      </c>
+      <c r="R10" t="n">
+        <v>68000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>81</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>282</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>24000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7575000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>283</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xdpX3Q36</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45618.625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Im9H9ezS</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45618.70833333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SMfm4Zck</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45619.54166666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GryrQGK8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45619.625</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
